--- a/AC_2018/AC_030_30-Manakondur_(SC).xlsx
+++ b/AC_2018/AC_030_30-Manakondur_(SC).xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -50,6 +50,11 @@
       <name val="Calibri"/>
       <color rgb="00000000"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="7">
@@ -90,7 +95,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -154,11 +159,19 @@
         <color rgb="001B365D"/>
       </bottom>
     </border>
+    <border>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom style="double">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -199,6 +212,23 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="6" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -841,7 +871,7 @@
         <v>4</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>709</v>
+        <v>698</v>
       </c>
       <c r="Q7" s="4" t="n">
         <v>0</v>
@@ -850,7 +880,7 @@
         <v>0</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>713</v>
+        <v>698</v>
       </c>
       <c r="T7" s="4" t="n">
         <v>0</v>
@@ -909,7 +939,7 @@
         <v>3</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="Q8" s="4" t="n">
         <v>0</v>
@@ -918,7 +948,7 @@
         <v>7</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>651</v>
+        <v>639</v>
       </c>
       <c r="T8" s="4" t="n">
         <v>0</v>
@@ -1045,7 +1075,7 @@
         <v>0</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>571</v>
+        <v>567</v>
       </c>
       <c r="Q10" s="4" t="n">
         <v>0</v>
@@ -1054,7 +1084,7 @@
         <v>15</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>586</v>
+        <v>582</v>
       </c>
       <c r="T10" s="4" t="n">
         <v>0</v>
@@ -1113,7 +1143,7 @@
         <v>5</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>549</v>
+        <v>544</v>
       </c>
       <c r="Q11" s="4" t="n">
         <v>0</v>
@@ -1122,7 +1152,7 @@
         <v>11</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>560</v>
+        <v>555</v>
       </c>
       <c r="T11" s="4" t="n">
         <v>0</v>
@@ -1181,7 +1211,7 @@
         <v>2</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>541</v>
+        <v>527</v>
       </c>
       <c r="Q12" s="4" t="n">
         <v>0</v>
@@ -1190,7 +1220,7 @@
         <v>8</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>549</v>
+        <v>535</v>
       </c>
       <c r="T12" s="4" t="n">
         <v>0</v>
@@ -1317,7 +1347,7 @@
         <v>2</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="Q14" s="4" t="n">
         <v>0</v>
@@ -1326,7 +1356,7 @@
         <v>9</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="T14" s="4" t="n">
         <v>0</v>
@@ -1453,7 +1483,7 @@
         <v>5</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="Q16" s="4" t="n">
         <v>0</v>
@@ -1462,7 +1492,7 @@
         <v>8</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>532</v>
+        <v>527</v>
       </c>
       <c r="T16" s="4" t="n">
         <v>0</v>
@@ -1589,7 +1619,7 @@
         <v>1</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="Q18" s="4" t="n">
         <v>0</v>
@@ -1598,7 +1628,7 @@
         <v>8</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>789</v>
+        <v>786</v>
       </c>
       <c r="T18" s="4" t="n">
         <v>0</v>
@@ -1725,7 +1755,7 @@
         <v>4</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>760</v>
+        <v>755</v>
       </c>
       <c r="Q20" s="4" t="n">
         <v>0</v>
@@ -1734,7 +1764,7 @@
         <v>16</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>776</v>
+        <v>771</v>
       </c>
       <c r="T20" s="4" t="n">
         <v>0</v>
@@ -1793,7 +1823,7 @@
         <v>0</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="Q21" s="4" t="n">
         <v>0</v>
@@ -1802,7 +1832,7 @@
         <v>9</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="T21" s="4" t="n">
         <v>0</v>
@@ -1861,7 +1891,7 @@
         <v>4</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>675</v>
+        <v>641</v>
       </c>
       <c r="Q22" s="4" t="n">
         <v>0</v>
@@ -1870,7 +1900,7 @@
         <v>7</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>682</v>
+        <v>648</v>
       </c>
       <c r="T22" s="4" t="n">
         <v>0</v>
@@ -1929,7 +1959,7 @@
         <v>4</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="Q23" s="4" t="n">
         <v>0</v>
@@ -1938,7 +1968,7 @@
         <v>5</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="T23" s="4" t="n">
         <v>0</v>
@@ -1997,7 +2027,7 @@
         <v>3</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>73</v>
+        <v>713</v>
       </c>
       <c r="Q24" s="4" t="n">
         <v>0</v>
@@ -2065,7 +2095,7 @@
         <v>4</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="Q25" s="4" t="n">
         <v>0</v>
@@ -2074,7 +2104,7 @@
         <v>13</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="T25" s="4" t="n">
         <v>0</v>
@@ -2201,7 +2231,7 @@
         <v>3</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>529</v>
+        <v>458</v>
       </c>
       <c r="Q27" s="4" t="n">
         <v>0</v>
@@ -2210,7 +2240,7 @@
         <v>8</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>537</v>
+        <v>466</v>
       </c>
       <c r="T27" s="4" t="n">
         <v>0</v>
@@ -2269,7 +2299,7 @@
         <v>2</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="Q28" s="4" t="n">
         <v>0</v>
@@ -2278,7 +2308,7 @@
         <v>16</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="T28" s="4" t="n">
         <v>0</v>
@@ -2337,7 +2367,7 @@
         <v>1</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="Q29" s="4" t="n">
         <v>0</v>
@@ -2346,7 +2376,7 @@
         <v>7</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="T29" s="4" t="n">
         <v>0</v>
@@ -2405,7 +2435,7 @@
         <v>3</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="Q30" s="4" t="n">
         <v>0</v>
@@ -2414,7 +2444,7 @@
         <v>10</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="T30" s="4" t="n">
         <v>0</v>
@@ -2541,7 +2571,7 @@
         <v>0</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>3876</v>
+        <v>876</v>
       </c>
       <c r="Q32" s="4" t="n">
         <v>0</v>
@@ -2618,7 +2648,7 @@
         <v>15</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>855</v>
+        <v>841</v>
       </c>
       <c r="T33" s="4" t="n">
         <v>0</v>
@@ -2745,7 +2775,7 @@
         <v>0</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>400</v>
+        <v>380</v>
       </c>
       <c r="Q35" s="4" t="n">
         <v>0</v>
@@ -2754,7 +2784,7 @@
         <v>0</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>404</v>
+        <v>380</v>
       </c>
       <c r="T35" s="4" t="n">
         <v>0</v>
@@ -2813,7 +2843,7 @@
         <v>3</v>
       </c>
       <c r="P36" s="4" t="n">
-        <v>990</v>
+        <v>980</v>
       </c>
       <c r="Q36" s="4" t="n">
         <v>0</v>
@@ -2822,7 +2852,7 @@
         <v>11</v>
       </c>
       <c r="S36" s="4" t="n">
-        <v>1001</v>
+        <v>991</v>
       </c>
       <c r="T36" s="4" t="n">
         <v>0</v>
@@ -2881,7 +2911,7 @@
         <v>11</v>
       </c>
       <c r="P37" s="4" t="n">
-        <v>882</v>
+        <v>872</v>
       </c>
       <c r="Q37" s="4" t="n">
         <v>0</v>
@@ -2890,7 +2920,7 @@
         <v>13</v>
       </c>
       <c r="S37" s="4" t="n">
-        <v>895</v>
+        <v>885</v>
       </c>
       <c r="T37" s="4" t="n">
         <v>0</v>
@@ -2949,7 +2979,7 @@
         <v>2</v>
       </c>
       <c r="P38" s="4" t="n">
-        <v>643</v>
+        <v>612</v>
       </c>
       <c r="Q38" s="4" t="n">
         <v>0</v>
@@ -2958,7 +2988,7 @@
         <v>16</v>
       </c>
       <c r="S38" s="4" t="n">
-        <v>659</v>
+        <v>628</v>
       </c>
       <c r="T38" s="4" t="n">
         <v>0</v>
@@ -3017,7 +3047,7 @@
         <v>0</v>
       </c>
       <c r="P39" s="4" t="n">
-        <v>355</v>
+        <v>317</v>
       </c>
       <c r="Q39" s="4" t="n">
         <v>0</v>
@@ -3026,7 +3056,7 @@
         <v>6</v>
       </c>
       <c r="S39" s="4" t="n">
-        <v>361</v>
+        <v>323</v>
       </c>
       <c r="T39" s="4" t="n">
         <v>0</v>
@@ -3153,7 +3183,7 @@
         <v>3</v>
       </c>
       <c r="P41" s="4" t="n">
-        <v>439</v>
+        <v>430</v>
       </c>
       <c r="Q41" s="4" t="n">
         <v>0</v>
@@ -3162,7 +3192,7 @@
         <v>0</v>
       </c>
       <c r="S41" s="4" t="n">
-        <v>450</v>
+        <v>430</v>
       </c>
       <c r="T41" s="4" t="n">
         <v>0</v>
@@ -3230,7 +3260,7 @@
         <v>0</v>
       </c>
       <c r="S42" s="4" t="n">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="T42" s="4" t="n">
         <v>0</v>
@@ -3426,7 +3456,7 @@
         <v>0</v>
       </c>
       <c r="P45" s="4" t="n">
-        <v>741</v>
+        <v>737</v>
       </c>
       <c r="Q45" s="4" t="n">
         <v>0</v>
@@ -3435,7 +3465,7 @@
         <v>14</v>
       </c>
       <c r="S45" s="4" t="n">
-        <v>755</v>
+        <v>751</v>
       </c>
       <c r="T45" s="4" t="n">
         <v>0</v>
@@ -3494,7 +3524,7 @@
         <v>7</v>
       </c>
       <c r="P46" s="4" t="n">
-        <v>819</v>
+        <v>809</v>
       </c>
       <c r="Q46" s="4" t="n">
         <v>0</v>
@@ -3503,7 +3533,7 @@
         <v>21</v>
       </c>
       <c r="S46" s="4" t="n">
-        <v>840</v>
+        <v>830</v>
       </c>
       <c r="T46" s="4" t="n">
         <v>0</v>
@@ -3562,7 +3592,7 @@
         <v>0</v>
       </c>
       <c r="P47" s="4" t="n">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="Q47" s="4" t="n">
         <v>0</v>
@@ -3571,7 +3601,7 @@
         <v>3</v>
       </c>
       <c r="S47" s="4" t="n">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="T47" s="4" t="n">
         <v>0</v>
@@ -3630,7 +3660,7 @@
         <v>0</v>
       </c>
       <c r="P48" s="4" t="n">
-        <v>626</v>
+        <v>325</v>
       </c>
       <c r="Q48" s="4" t="n">
         <v>0</v>
@@ -3639,7 +3669,7 @@
         <v>7</v>
       </c>
       <c r="S48" s="4" t="n">
-        <v>633</v>
+        <v>332</v>
       </c>
       <c r="T48" s="4" t="n">
         <v>0</v>
@@ -3834,7 +3864,7 @@
         <v>3</v>
       </c>
       <c r="P51" s="4" t="n">
-        <v>558</v>
+        <v>548</v>
       </c>
       <c r="Q51" s="4" t="n">
         <v>0</v>
@@ -3843,7 +3873,7 @@
         <v>14</v>
       </c>
       <c r="S51" s="4" t="n">
-        <v>572</v>
+        <v>562</v>
       </c>
       <c r="T51" s="4" t="n">
         <v>0</v>
@@ -3902,7 +3932,7 @@
         <v>6</v>
       </c>
       <c r="P52" s="4" t="n">
-        <v>750</v>
+        <v>747</v>
       </c>
       <c r="Q52" s="4" t="n">
         <v>0</v>
@@ -3911,7 +3941,7 @@
         <v>7</v>
       </c>
       <c r="S52" s="4" t="n">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="T52" s="4" t="n">
         <v>0</v>
@@ -3970,7 +4000,7 @@
         <v>5</v>
       </c>
       <c r="P53" s="4" t="n">
-        <v>724</v>
+        <v>706</v>
       </c>
       <c r="Q53" s="4" t="n">
         <v>0</v>
@@ -3979,7 +4009,7 @@
         <v>21</v>
       </c>
       <c r="S53" s="4" t="n">
-        <v>745</v>
+        <v>727</v>
       </c>
       <c r="T53" s="4" t="n">
         <v>0</v>
@@ -4038,7 +4068,7 @@
         <v>0</v>
       </c>
       <c r="P54" s="4" t="n">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="Q54" s="4" t="n">
         <v>0</v>
@@ -4047,7 +4077,7 @@
         <v>11</v>
       </c>
       <c r="S54" s="4" t="n">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="T54" s="4" t="n">
         <v>0</v>
@@ -4174,7 +4204,7 @@
         <v>0</v>
       </c>
       <c r="P56" s="4" t="n">
-        <v>764</v>
+        <v>708</v>
       </c>
       <c r="Q56" s="4" t="n">
         <v>0</v>
@@ -4183,7 +4213,7 @@
         <v>14</v>
       </c>
       <c r="S56" s="4" t="n">
-        <v>778</v>
+        <v>722</v>
       </c>
       <c r="T56" s="4" t="n">
         <v>0</v>
@@ -4242,7 +4272,7 @@
         <v>5</v>
       </c>
       <c r="P57" s="4" t="n">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="Q57" s="4" t="n">
         <v>0</v>
@@ -4251,7 +4281,7 @@
         <v>11</v>
       </c>
       <c r="S57" s="4" t="n">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="T57" s="4" t="n">
         <v>0</v>
@@ -4310,7 +4340,7 @@
         <v>0</v>
       </c>
       <c r="P58" s="4" t="n">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="Q58" s="4" t="n">
         <v>0</v>
@@ -4319,7 +4349,7 @@
         <v>9</v>
       </c>
       <c r="S58" s="4" t="n">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="T58" s="4" t="n">
         <v>0</v>
@@ -4378,7 +4408,7 @@
         <v>4</v>
       </c>
       <c r="P59" s="4" t="n">
-        <v>796</v>
+        <v>746</v>
       </c>
       <c r="Q59" s="4" t="n">
         <v>0</v>
@@ -4387,7 +4417,7 @@
         <v>25</v>
       </c>
       <c r="S59" s="4" t="n">
-        <v>821</v>
+        <v>771</v>
       </c>
       <c r="T59" s="4" t="n">
         <v>0</v>
@@ -4455,7 +4485,7 @@
         <v>1</v>
       </c>
       <c r="S60" s="4" t="n">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="T60" s="4" t="n">
         <v>0</v>
@@ -4514,7 +4544,7 @@
         <v>0</v>
       </c>
       <c r="P61" s="4" t="n">
-        <v>787</v>
+        <v>782</v>
       </c>
       <c r="Q61" s="4" t="n">
         <v>0</v>
@@ -4523,7 +4553,7 @@
         <v>2</v>
       </c>
       <c r="S61" s="4" t="n">
-        <v>789</v>
+        <v>784</v>
       </c>
       <c r="T61" s="4" t="n">
         <v>0</v>
@@ -4582,7 +4612,7 @@
         <v>0</v>
       </c>
       <c r="P62" s="4" t="n">
-        <v>728</v>
+        <v>724</v>
       </c>
       <c r="Q62" s="4" t="n">
         <v>0</v>
@@ -4591,7 +4621,7 @@
         <v>10</v>
       </c>
       <c r="S62" s="4" t="n">
-        <v>738</v>
+        <v>734</v>
       </c>
       <c r="T62" s="4" t="n">
         <v>0</v>
@@ -4659,7 +4689,7 @@
         <v>23</v>
       </c>
       <c r="S63" s="4" t="n">
-        <v>625</v>
+        <v>635</v>
       </c>
       <c r="T63" s="4" t="n">
         <v>0</v>
@@ -4718,7 +4748,7 @@
         <v>0</v>
       </c>
       <c r="P64" s="4" t="n">
-        <v>916</v>
+        <v>901</v>
       </c>
       <c r="Q64" s="4" t="n">
         <v>0</v>
@@ -4727,7 +4757,7 @@
         <v>37</v>
       </c>
       <c r="S64" s="4" t="n">
-        <v>953</v>
+        <v>938</v>
       </c>
       <c r="T64" s="4" t="n">
         <v>0</v>
@@ -4922,7 +4952,7 @@
         <v>0</v>
       </c>
       <c r="P67" s="4" t="n">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="Q67" s="4" t="n">
         <v>0</v>
@@ -4931,7 +4961,7 @@
         <v>6</v>
       </c>
       <c r="S67" s="4" t="n">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="T67" s="4" t="n">
         <v>0</v>
@@ -5058,7 +5088,7 @@
         <v>2</v>
       </c>
       <c r="P69" s="4" t="n">
-        <v>916</v>
+        <v>910</v>
       </c>
       <c r="Q69" s="4" t="n">
         <v>0</v>
@@ -5067,7 +5097,7 @@
         <v>11</v>
       </c>
       <c r="S69" s="4" t="n">
-        <v>927</v>
+        <v>921</v>
       </c>
       <c r="T69" s="4" t="n">
         <v>0</v>
@@ -5126,7 +5156,7 @@
         <v>0</v>
       </c>
       <c r="P70" s="4" t="n">
-        <v>896</v>
+        <v>882</v>
       </c>
       <c r="Q70" s="4" t="n">
         <v>0</v>
@@ -5135,7 +5165,7 @@
         <v>18</v>
       </c>
       <c r="S70" s="4" t="n">
-        <v>914</v>
+        <v>900</v>
       </c>
       <c r="T70" s="4" t="n">
         <v>0</v>
@@ -5194,7 +5224,7 @@
         <v>0</v>
       </c>
       <c r="P71" s="4" t="n">
-        <v>899</v>
+        <v>893</v>
       </c>
       <c r="Q71" s="4" t="n">
         <v>0</v>
@@ -5203,7 +5233,7 @@
         <v>7</v>
       </c>
       <c r="S71" s="4" t="n">
-        <v>916</v>
+        <v>900</v>
       </c>
       <c r="T71" s="4" t="n">
         <v>0</v>
@@ -5262,7 +5292,7 @@
         <v>4</v>
       </c>
       <c r="P72" s="4" t="n">
-        <v>686</v>
+        <v>698</v>
       </c>
       <c r="Q72" s="4" t="n">
         <v>0</v>
@@ -5271,7 +5301,7 @@
         <v>0</v>
       </c>
       <c r="S72" s="4" t="n">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="T72" s="4" t="n">
         <v>0</v>
@@ -5330,7 +5360,7 @@
         <v>0</v>
       </c>
       <c r="P73" s="4" t="n">
-        <v>504</v>
+        <v>494</v>
       </c>
       <c r="Q73" s="4" t="n">
         <v>0</v>
@@ -5339,7 +5369,7 @@
         <v>2</v>
       </c>
       <c r="S73" s="4" t="n">
-        <v>506</v>
+        <v>496</v>
       </c>
       <c r="T73" s="4" t="n">
         <v>0</v>
@@ -5398,7 +5428,7 @@
         <v>0</v>
       </c>
       <c r="P74" s="4" t="n">
-        <v>648</v>
+        <v>598</v>
       </c>
       <c r="Q74" s="4" t="n">
         <v>0</v>
@@ -5407,7 +5437,7 @@
         <v>0</v>
       </c>
       <c r="S74" s="4" t="n">
-        <v>653</v>
+        <v>598</v>
       </c>
       <c r="T74" s="4" t="n">
         <v>0</v>
@@ -5466,7 +5496,7 @@
         <v>0</v>
       </c>
       <c r="P75" s="4" t="n">
-        <v>389</v>
+        <v>489</v>
       </c>
       <c r="Q75" s="4" t="n">
         <v>0</v>
@@ -5475,7 +5505,7 @@
         <v>3</v>
       </c>
       <c r="S75" s="4" t="n">
-        <v>392</v>
+        <v>492</v>
       </c>
       <c r="T75" s="4" t="n">
         <v>0</v>
@@ -5670,7 +5700,7 @@
         <v>8</v>
       </c>
       <c r="P78" s="4" t="n">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="Q78" s="4" t="n">
         <v>0</v>
@@ -5679,7 +5709,7 @@
         <v>14</v>
       </c>
       <c r="S78" s="4" t="n">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="T78" s="4" t="n">
         <v>0</v>
@@ -5738,7 +5768,7 @@
         <v>1</v>
       </c>
       <c r="P79" s="4" t="n">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="Q79" s="4" t="n">
         <v>0</v>
@@ -5747,7 +5777,7 @@
         <v>8</v>
       </c>
       <c r="S79" s="4" t="n">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="T79" s="4" t="n">
         <v>0</v>
@@ -5883,7 +5913,7 @@
         <v>7</v>
       </c>
       <c r="S81" s="4" t="n">
-        <v>939</v>
+        <v>929</v>
       </c>
       <c r="T81" s="4" t="n">
         <v>0</v>
@@ -5951,7 +5981,7 @@
         <v>23</v>
       </c>
       <c r="S82" s="4" t="n">
-        <v>680</v>
+        <v>690</v>
       </c>
       <c r="T82" s="4" t="n">
         <v>0</v>
@@ -6010,7 +6040,7 @@
         <v>3</v>
       </c>
       <c r="P83" s="4" t="n">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="Q83" s="4" t="n">
         <v>0</v>
@@ -6019,7 +6049,7 @@
         <v>25</v>
       </c>
       <c r="S83" s="4" t="n">
-        <v>668</v>
+        <v>665</v>
       </c>
       <c r="T83" s="4" t="n">
         <v>0</v>
@@ -6078,7 +6108,7 @@
         <v>2</v>
       </c>
       <c r="P84" s="4" t="n">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="Q84" s="4" t="n">
         <v>0</v>
@@ -6087,7 +6117,7 @@
         <v>5</v>
       </c>
       <c r="S84" s="4" t="n">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="T84" s="4" t="n">
         <v>0</v>
@@ -6146,7 +6176,7 @@
         <v>4</v>
       </c>
       <c r="P85" s="4" t="n">
-        <v>309</v>
+        <v>809</v>
       </c>
       <c r="Q85" s="4" t="n">
         <v>0</v>
@@ -6350,7 +6380,7 @@
         <v>37</v>
       </c>
       <c r="P88" s="4" t="n">
-        <v>772</v>
+        <v>839</v>
       </c>
       <c r="Q88" s="4" t="n">
         <v>0</v>
@@ -6359,7 +6389,7 @@
         <v>11</v>
       </c>
       <c r="S88" s="4" t="n">
-        <v>783</v>
+        <v>850</v>
       </c>
       <c r="T88" s="4" t="n">
         <v>0</v>
@@ -6418,7 +6448,7 @@
         <v>2</v>
       </c>
       <c r="P89" s="4" t="n">
-        <v>615</v>
+        <v>585</v>
       </c>
       <c r="Q89" s="4" t="n">
         <v>0</v>
@@ -6427,7 +6457,7 @@
         <v>8</v>
       </c>
       <c r="S89" s="4" t="n">
-        <v>623</v>
+        <v>593</v>
       </c>
       <c r="T89" s="4" t="n">
         <v>0</v>
@@ -6486,7 +6516,7 @@
         <v>0</v>
       </c>
       <c r="P90" s="4" t="n">
-        <v>566</v>
+        <v>596</v>
       </c>
       <c r="Q90" s="4" t="n">
         <v>0</v>
@@ -6495,7 +6525,7 @@
         <v>19</v>
       </c>
       <c r="S90" s="4" t="n">
-        <v>585</v>
+        <v>615</v>
       </c>
       <c r="T90" s="4" t="n">
         <v>0</v>
@@ -6554,7 +6584,7 @@
         <v>3</v>
       </c>
       <c r="P91" s="4" t="n">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="Q91" s="4" t="n">
         <v>0</v>
@@ -6563,7 +6593,7 @@
         <v>6</v>
       </c>
       <c r="S91" s="4" t="n">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="T91" s="4" t="n">
         <v>0</v>
@@ -6622,7 +6652,7 @@
         <v>0</v>
       </c>
       <c r="P92" s="4" t="n">
-        <v>997</v>
+        <v>995</v>
       </c>
       <c r="Q92" s="4" t="n">
         <v>0</v>
@@ -6631,7 +6661,7 @@
         <v>16</v>
       </c>
       <c r="S92" s="4" t="n">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="T92" s="4" t="n">
         <v>0</v>
@@ -6690,7 +6720,7 @@
         <v>37</v>
       </c>
       <c r="P93" s="4" t="n">
-        <v>696</v>
+        <v>720</v>
       </c>
       <c r="Q93" s="4" t="n">
         <v>0</v>
@@ -6699,7 +6729,7 @@
         <v>8</v>
       </c>
       <c r="S93" s="4" t="n">
-        <v>704</v>
+        <v>728</v>
       </c>
       <c r="T93" s="4" t="n">
         <v>0</v>
@@ -6758,7 +6788,7 @@
         <v>1</v>
       </c>
       <c r="P94" s="4" t="n">
-        <v>71</v>
+        <v>701</v>
       </c>
       <c r="Q94" s="4" t="n">
         <v>0</v>
@@ -6767,7 +6797,7 @@
         <v>9</v>
       </c>
       <c r="S94" s="4" t="n">
-        <v>720</v>
+        <v>710</v>
       </c>
       <c r="T94" s="4" t="n">
         <v>0</v>
@@ -6827,7 +6857,7 @@
         <v>2</v>
       </c>
       <c r="P95" s="4" t="n">
-        <v>667</v>
+        <v>663</v>
       </c>
       <c r="Q95" s="4" t="n">
         <v>0</v>
@@ -6836,7 +6866,7 @@
         <v>5</v>
       </c>
       <c r="S95" s="4" t="n">
-        <v>672</v>
+        <v>668</v>
       </c>
       <c r="T95" s="4" t="n">
         <v>0</v>
@@ -7031,7 +7061,7 @@
         <v>0</v>
       </c>
       <c r="P98" s="4" t="n">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="Q98" s="4" t="n">
         <v>0</v>
@@ -7040,7 +7070,7 @@
         <v>11</v>
       </c>
       <c r="S98" s="4" t="n">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="T98" s="4" t="n">
         <v>0</v>
@@ -7167,7 +7197,7 @@
         <v>2</v>
       </c>
       <c r="P100" s="4" t="n">
-        <v>473</v>
+        <v>463</v>
       </c>
       <c r="Q100" s="4" t="n">
         <v>0</v>
@@ -7176,7 +7206,7 @@
         <v>6</v>
       </c>
       <c r="S100" s="4" t="n">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="T100" s="4" t="n">
         <v>0</v>
@@ -7303,7 +7333,7 @@
         <v>3</v>
       </c>
       <c r="P102" s="4" t="n">
-        <v>835</v>
+        <v>783</v>
       </c>
       <c r="Q102" s="4" t="n">
         <v>0</v>
@@ -7312,7 +7342,7 @@
         <v>16</v>
       </c>
       <c r="S102" s="4" t="n">
-        <v>851</v>
+        <v>799</v>
       </c>
       <c r="T102" s="4" t="n">
         <v>0</v>
@@ -7371,7 +7401,7 @@
         <v>0</v>
       </c>
       <c r="P103" s="4" t="n">
-        <v>856</v>
+        <v>844</v>
       </c>
       <c r="Q103" s="4" t="n">
         <v>0</v>
@@ -7380,7 +7410,7 @@
         <v>1</v>
       </c>
       <c r="S103" s="4" t="n">
-        <v>867</v>
+        <v>845</v>
       </c>
       <c r="T103" s="4" t="n">
         <v>0</v>
@@ -7643,7 +7673,7 @@
         <v>0</v>
       </c>
       <c r="P107" s="4" t="n">
-        <v>366</v>
+        <v>373</v>
       </c>
       <c r="Q107" s="4" t="n">
         <v>0</v>
@@ -7652,7 +7682,7 @@
         <v>10</v>
       </c>
       <c r="S107" s="4" t="n">
-        <v>376</v>
+        <v>383</v>
       </c>
       <c r="T107" s="4" t="n">
         <v>0</v>
@@ -7711,7 +7741,7 @@
         <v>4</v>
       </c>
       <c r="P108" s="4" t="n">
-        <v>710</v>
+        <v>713</v>
       </c>
       <c r="Q108" s="4" t="n">
         <v>0</v>
@@ -7720,7 +7750,7 @@
         <v>8</v>
       </c>
       <c r="S108" s="4" t="n">
-        <v>718</v>
+        <v>721</v>
       </c>
       <c r="T108" s="4" t="n">
         <v>0</v>
@@ -7779,7 +7809,7 @@
         <v>0</v>
       </c>
       <c r="P109" s="4" t="n">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="Q109" s="4" t="n">
         <v>0</v>
@@ -7788,7 +7818,7 @@
         <v>0</v>
       </c>
       <c r="S109" s="4" t="n">
-        <v>619</v>
+        <v>610</v>
       </c>
       <c r="T109" s="4" t="n">
         <v>0</v>
@@ -7847,7 +7877,7 @@
         <v>4</v>
       </c>
       <c r="P110" s="4" t="n">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="Q110" s="4" t="n">
         <v>0</v>
@@ -7856,7 +7886,7 @@
         <v>9</v>
       </c>
       <c r="S110" s="4" t="n">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="T110" s="4" t="n">
         <v>0</v>
@@ -7983,7 +8013,7 @@
         <v>0</v>
       </c>
       <c r="P112" s="4" t="n">
-        <v>266</v>
+        <v>253</v>
       </c>
       <c r="Q112" s="4" t="n">
         <v>0</v>
@@ -7992,7 +8022,7 @@
         <v>0</v>
       </c>
       <c r="S112" s="4" t="n">
-        <v>270</v>
+        <v>253</v>
       </c>
       <c r="T112" s="4" t="n">
         <v>0</v>
@@ -8255,7 +8285,7 @@
         <v>2</v>
       </c>
       <c r="P116" s="4" t="n">
-        <v>539</v>
+        <v>524</v>
       </c>
       <c r="Q116" s="4" t="n">
         <v>0</v>
@@ -8264,7 +8294,7 @@
         <v>7</v>
       </c>
       <c r="S116" s="4" t="n">
-        <v>546</v>
+        <v>531</v>
       </c>
       <c r="T116" s="4" t="n">
         <v>0</v>
@@ -8392,7 +8422,7 @@
         <v>3</v>
       </c>
       <c r="P118" s="4" t="n">
-        <v>922</v>
+        <v>915</v>
       </c>
       <c r="Q118" s="4" t="n">
         <v>0</v>
@@ -8401,7 +8431,7 @@
         <v>16</v>
       </c>
       <c r="S118" s="4" t="n">
-        <v>938</v>
+        <v>931</v>
       </c>
       <c r="T118" s="4" t="n">
         <v>0</v>
@@ -8460,7 +8490,7 @@
         <v>3</v>
       </c>
       <c r="P119" s="4" t="n">
-        <v>975</v>
+        <v>970</v>
       </c>
       <c r="Q119" s="4" t="n">
         <v>0</v>
@@ -8469,7 +8499,7 @@
         <v>12</v>
       </c>
       <c r="S119" s="4" t="n">
-        <v>987</v>
+        <v>982</v>
       </c>
       <c r="T119" s="4" t="n">
         <v>0</v>
@@ -8596,7 +8626,7 @@
         <v>0</v>
       </c>
       <c r="P121" s="4" t="n">
-        <v>74</v>
+        <v>574</v>
       </c>
       <c r="Q121" s="4" t="n">
         <v>0</v>
@@ -8664,7 +8694,7 @@
         <v>2</v>
       </c>
       <c r="P122" s="4" t="n">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="Q122" s="4" t="n">
         <v>0</v>
@@ -8673,7 +8703,7 @@
         <v>12</v>
       </c>
       <c r="S122" s="4" t="n">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="T122" s="4" t="n">
         <v>0</v>
@@ -8800,7 +8830,7 @@
         <v>0</v>
       </c>
       <c r="P124" s="4" t="n">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="Q124" s="4" t="n">
         <v>0</v>
@@ -8809,7 +8839,7 @@
         <v>10</v>
       </c>
       <c r="S124" s="4" t="n">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="T124" s="4" t="n">
         <v>0</v>
@@ -8936,7 +8966,7 @@
         <v>0</v>
       </c>
       <c r="P126" s="4" t="n">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="Q126" s="4" t="n">
         <v>0</v>
@@ -8945,7 +8975,7 @@
         <v>4</v>
       </c>
       <c r="S126" s="4" t="n">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="T126" s="4" t="n">
         <v>0</v>
@@ -9277,7 +9307,7 @@
         <v>4</v>
       </c>
       <c r="P131" s="4" t="n">
-        <v>600</v>
+        <v>596</v>
       </c>
       <c r="Q131" s="4" t="n">
         <v>0</v>
@@ -9286,7 +9316,7 @@
         <v>8</v>
       </c>
       <c r="S131" s="4" t="n">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="T131" s="4" t="n">
         <v>0</v>
@@ -9346,7 +9376,7 @@
         <v>2</v>
       </c>
       <c r="P132" s="4" t="n">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="Q132" s="4" t="n">
         <v>0</v>
@@ -9355,7 +9385,7 @@
         <v>12</v>
       </c>
       <c r="S132" s="4" t="n">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="T132" s="4" t="n">
         <v>1</v>
@@ -9414,7 +9444,7 @@
         <v>5</v>
       </c>
       <c r="P133" s="4" t="n">
-        <v>934</v>
+        <v>434</v>
       </c>
       <c r="Q133" s="4" t="n">
         <v>0</v>
@@ -9423,7 +9453,7 @@
         <v>13</v>
       </c>
       <c r="S133" s="4" t="n">
-        <v>947</v>
+        <v>447</v>
       </c>
       <c r="T133" s="4" t="n">
         <v>0</v>
@@ -9550,7 +9580,7 @@
         <v>5</v>
       </c>
       <c r="P135" s="4" t="n">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="Q135" s="4" t="n">
         <v>0</v>
@@ -9559,7 +9589,7 @@
         <v>10</v>
       </c>
       <c r="S135" s="4" t="n">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="T135" s="4" t="n">
         <v>0</v>
@@ -9618,7 +9648,7 @@
         <v>2</v>
       </c>
       <c r="P136" s="4" t="n">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="Q136" s="4" t="n">
         <v>0</v>
@@ -9627,7 +9657,7 @@
         <v>18</v>
       </c>
       <c r="S136" s="4" t="n">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="T136" s="4" t="n">
         <v>0</v>
@@ -9686,7 +9716,7 @@
         <v>3</v>
       </c>
       <c r="P137" s="4" t="n">
-        <v>496</v>
+        <v>448</v>
       </c>
       <c r="Q137" s="4" t="n">
         <v>0</v>
@@ -9695,7 +9725,7 @@
         <v>7</v>
       </c>
       <c r="S137" s="4" t="n">
-        <v>503</v>
+        <v>455</v>
       </c>
       <c r="T137" s="4" t="n">
         <v>0</v>
@@ -9754,7 +9784,7 @@
         <v>2</v>
       </c>
       <c r="P138" s="4" t="n">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="Q138" s="4" t="n">
         <v>0</v>
@@ -9763,7 +9793,7 @@
         <v>8</v>
       </c>
       <c r="S138" s="4" t="n">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="T138" s="4" t="n">
         <v>0</v>
@@ -9890,7 +9920,7 @@
         <v>2</v>
       </c>
       <c r="P140" s="4" t="n">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="Q140" s="4" t="n">
         <v>0</v>
@@ -9899,7 +9929,7 @@
         <v>1</v>
       </c>
       <c r="S140" s="4" t="n">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="T140" s="4" t="n">
         <v>0</v>
@@ -9958,7 +9988,7 @@
         <v>0</v>
       </c>
       <c r="P141" s="4" t="n">
-        <v>421</v>
+        <v>404</v>
       </c>
       <c r="Q141" s="4" t="n">
         <v>0</v>
@@ -9967,7 +9997,7 @@
         <v>4</v>
       </c>
       <c r="S141" s="4" t="n">
-        <v>425</v>
+        <v>408</v>
       </c>
       <c r="T141" s="4" t="n">
         <v>0</v>
@@ -10026,7 +10056,7 @@
         <v>4</v>
       </c>
       <c r="P142" s="4" t="n">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="Q142" s="4" t="n">
         <v>0</v>
@@ -10035,7 +10065,7 @@
         <v>12</v>
       </c>
       <c r="S142" s="4" t="n">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="T142" s="4" t="n">
         <v>0</v>
@@ -10094,7 +10124,7 @@
         <v>4</v>
       </c>
       <c r="P143" s="4" t="n">
-        <v>621</v>
+        <v>627</v>
       </c>
       <c r="Q143" s="4" t="n">
         <v>0</v>
@@ -10103,7 +10133,7 @@
         <v>6</v>
       </c>
       <c r="S143" s="4" t="n">
-        <v>627</v>
+        <v>633</v>
       </c>
       <c r="T143" s="4" t="n">
         <v>0</v>
@@ -10162,7 +10192,7 @@
         <v>3</v>
       </c>
       <c r="P144" s="4" t="n">
-        <v>66</v>
+        <v>654</v>
       </c>
       <c r="Q144" s="4" t="n">
         <v>0</v>
@@ -10171,7 +10201,7 @@
         <v>10</v>
       </c>
       <c r="S144" s="4" t="n">
-        <v>675</v>
+        <v>664</v>
       </c>
       <c r="T144" s="4" t="n">
         <v>0</v>
@@ -10230,7 +10260,7 @@
         <v>0</v>
       </c>
       <c r="P145" s="4" t="n">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="Q145" s="4" t="n">
         <v>0</v>
@@ -10239,7 +10269,7 @@
         <v>0</v>
       </c>
       <c r="S145" s="4" t="n">
-        <v>614</v>
+        <v>595</v>
       </c>
       <c r="T145" s="4" t="n">
         <v>0</v>
@@ -10366,7 +10396,7 @@
         <v>0</v>
       </c>
       <c r="P147" s="4" t="n">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="Q147" s="4" t="n">
         <v>0</v>
@@ -10434,7 +10464,7 @@
         <v>2</v>
       </c>
       <c r="P148" s="4" t="n">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="Q148" s="4" t="n">
         <v>0</v>
@@ -10443,7 +10473,7 @@
         <v>7</v>
       </c>
       <c r="S148" s="4" t="n">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="T148" s="4" t="n">
         <v>0</v>
@@ -10502,7 +10532,7 @@
         <v>3</v>
       </c>
       <c r="P149" s="4" t="n">
-        <v>866</v>
+        <v>863</v>
       </c>
       <c r="Q149" s="4" t="n">
         <v>0</v>
@@ -10511,7 +10541,7 @@
         <v>7</v>
       </c>
       <c r="S149" s="4" t="n">
-        <v>873</v>
+        <v>870</v>
       </c>
       <c r="T149" s="4" t="n">
         <v>0</v>
@@ -10638,7 +10668,7 @@
         <v>1</v>
       </c>
       <c r="P151" s="4" t="n">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="Q151" s="4" t="n">
         <v>0</v>
@@ -10647,7 +10677,7 @@
         <v>6</v>
       </c>
       <c r="S151" s="4" t="n">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="T151" s="4" t="n">
         <v>0</v>
@@ -10706,7 +10736,7 @@
         <v>1</v>
       </c>
       <c r="P152" s="4" t="n">
-        <v>947</v>
+        <v>937</v>
       </c>
       <c r="Q152" s="4" t="n">
         <v>0</v>
@@ -10715,7 +10745,7 @@
         <v>22</v>
       </c>
       <c r="S152" s="4" t="n">
-        <v>969</v>
+        <v>959</v>
       </c>
       <c r="T152" s="4" t="n">
         <v>0</v>
@@ -11251,7 +11281,7 @@
         <v>3</v>
       </c>
       <c r="P160" s="4" t="n">
-        <v>754</v>
+        <v>853</v>
       </c>
       <c r="Q160" s="4" t="n">
         <v>0</v>
@@ -11260,7 +11290,7 @@
         <v>8</v>
       </c>
       <c r="S160" s="4" t="n">
-        <v>762</v>
+        <v>861</v>
       </c>
       <c r="T160" s="4" t="n">
         <v>0</v>
@@ -11319,7 +11349,7 @@
         <v>0</v>
       </c>
       <c r="P161" s="4" t="n">
-        <v>618</v>
+        <v>607</v>
       </c>
       <c r="Q161" s="4" t="n">
         <v>0</v>
@@ -11328,7 +11358,7 @@
         <v>7</v>
       </c>
       <c r="S161" s="4" t="n">
-        <v>625</v>
+        <v>614</v>
       </c>
       <c r="T161" s="4" t="n">
         <v>0</v>
@@ -11464,7 +11494,7 @@
         <v>0</v>
       </c>
       <c r="S163" s="4" t="n">
-        <v>498</v>
+        <v>489</v>
       </c>
       <c r="T163" s="4" t="n">
         <v>0</v>
@@ -11591,7 +11621,7 @@
         <v>0</v>
       </c>
       <c r="P165" s="4" t="n">
-        <v>912</v>
+        <v>909</v>
       </c>
       <c r="Q165" s="4" t="n">
         <v>0</v>
@@ -11600,7 +11630,7 @@
         <v>12</v>
       </c>
       <c r="S165" s="4" t="n">
-        <v>924</v>
+        <v>921</v>
       </c>
       <c r="T165" s="4" t="n">
         <v>0</v>
@@ -11795,7 +11825,7 @@
         <v>0</v>
       </c>
       <c r="P168" s="4" t="n">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="Q168" s="4" t="n">
         <v>0</v>
@@ -11804,7 +11834,7 @@
         <v>3</v>
       </c>
       <c r="S168" s="4" t="n">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="T168" s="4" t="n">
         <v>0</v>
@@ -11863,7 +11893,7 @@
         <v>5</v>
       </c>
       <c r="P169" s="4" t="n">
-        <v>722</v>
+        <v>719</v>
       </c>
       <c r="Q169" s="4" t="n">
         <v>0</v>
@@ -11872,7 +11902,7 @@
         <v>15</v>
       </c>
       <c r="S169" s="4" t="n">
-        <v>737</v>
+        <v>734</v>
       </c>
       <c r="T169" s="4" t="n">
         <v>0</v>
@@ -11931,7 +11961,7 @@
         <v>0</v>
       </c>
       <c r="P170" s="4" t="n">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="Q170" s="4" t="n">
         <v>0</v>
@@ -11940,7 +11970,7 @@
         <v>5</v>
       </c>
       <c r="S170" s="4" t="n">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="T170" s="4" t="n">
         <v>0</v>
@@ -11999,7 +12029,7 @@
         <v>0</v>
       </c>
       <c r="P171" s="4" t="n">
-        <v>71</v>
+        <v>571</v>
       </c>
       <c r="Q171" s="4" t="n">
         <v>0</v>
@@ -12135,7 +12165,7 @@
         <v>0</v>
       </c>
       <c r="P173" s="4" t="n">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="Q173" s="4" t="n">
         <v>0</v>
@@ -12144,7 +12174,7 @@
         <v>3</v>
       </c>
       <c r="S173" s="4" t="n">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="T173" s="4" t="n">
         <v>0</v>
@@ -12203,7 +12233,7 @@
         <v>2</v>
       </c>
       <c r="P174" s="4" t="n">
-        <v>602</v>
+        <v>522</v>
       </c>
       <c r="Q174" s="4" t="n">
         <v>0</v>
@@ -12212,7 +12242,7 @@
         <v>8</v>
       </c>
       <c r="S174" s="4" t="n">
-        <v>610</v>
+        <v>530</v>
       </c>
       <c r="T174" s="4" t="n">
         <v>0</v>
@@ -12280,7 +12310,7 @@
         <v>0</v>
       </c>
       <c r="S175" s="4" t="n">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="T175" s="4" t="n">
         <v>0</v>
@@ -12339,7 +12369,7 @@
         <v>5</v>
       </c>
       <c r="P176" s="4" t="n">
-        <v>785</v>
+        <v>713</v>
       </c>
       <c r="Q176" s="4" t="n">
         <v>0</v>
@@ -12348,7 +12378,7 @@
         <v>123</v>
       </c>
       <c r="S176" s="4" t="n">
-        <v>798</v>
+        <v>836</v>
       </c>
       <c r="T176" s="4" t="n">
         <v>0</v>
@@ -12407,7 +12437,7 @@
         <v>5</v>
       </c>
       <c r="P177" s="4" t="n">
-        <v>857</v>
+        <v>875</v>
       </c>
       <c r="Q177" s="4" t="n">
         <v>0</v>
@@ -12416,7 +12446,7 @@
         <v>5</v>
       </c>
       <c r="S177" s="4" t="n">
-        <v>862</v>
+        <v>880</v>
       </c>
       <c r="T177" s="4" t="n">
         <v>0</v>
@@ -12475,7 +12505,7 @@
         <v>3</v>
       </c>
       <c r="P178" s="4" t="n">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="Q178" s="4" t="n">
         <v>0</v>
@@ -12484,7 +12514,7 @@
         <v>44</v>
       </c>
       <c r="S178" s="4" t="n">
-        <v>981</v>
+        <v>1010</v>
       </c>
       <c r="T178" s="4" t="n">
         <v>0</v>
@@ -12543,7 +12573,7 @@
         <v>0</v>
       </c>
       <c r="P179" s="4" t="n">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="Q179" s="4" t="n">
         <v>0</v>
@@ -12552,7 +12582,7 @@
         <v>2</v>
       </c>
       <c r="S179" s="4" t="n">
-        <v>975</v>
+        <v>964</v>
       </c>
       <c r="T179" s="4" t="n">
         <v>0</v>
@@ -12611,7 +12641,7 @@
         <v>2</v>
       </c>
       <c r="P180" s="4" t="n">
-        <v>612</v>
+        <v>595</v>
       </c>
       <c r="Q180" s="4" t="n">
         <v>0</v>
@@ -12620,7 +12650,7 @@
         <v>5</v>
       </c>
       <c r="S180" s="4" t="n">
-        <v>617</v>
+        <v>600</v>
       </c>
       <c r="T180" s="4" t="n">
         <v>0</v>
@@ -12679,7 +12709,7 @@
         <v>2</v>
       </c>
       <c r="P181" s="4" t="n">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="Q181" s="4" t="n">
         <v>0</v>
@@ -12688,7 +12718,7 @@
         <v>6</v>
       </c>
       <c r="S181" s="4" t="n">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="T181" s="4" t="n">
         <v>0</v>
@@ -12747,7 +12777,7 @@
         <v>1</v>
       </c>
       <c r="P182" s="4" t="n">
-        <v>898</v>
+        <v>896</v>
       </c>
       <c r="Q182" s="4" t="n">
         <v>0</v>
@@ -12756,7 +12786,7 @@
         <v>15</v>
       </c>
       <c r="S182" s="4" t="n">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="T182" s="4" t="n">
         <v>0</v>
@@ -12815,7 +12845,7 @@
         <v>0</v>
       </c>
       <c r="P183" s="4" t="n">
-        <v>887</v>
+        <v>835</v>
       </c>
       <c r="Q183" s="4" t="n">
         <v>0</v>
@@ -12824,7 +12854,7 @@
         <v>44</v>
       </c>
       <c r="S183" s="4" t="n">
-        <v>901</v>
+        <v>879</v>
       </c>
       <c r="T183" s="4" t="n">
         <v>0</v>
@@ -12883,7 +12913,7 @@
         <v>0</v>
       </c>
       <c r="P184" s="4" t="n">
-        <v>962</v>
+        <v>519</v>
       </c>
       <c r="Q184" s="4" t="n">
         <v>0</v>
@@ -12892,7 +12922,7 @@
         <v>12</v>
       </c>
       <c r="S184" s="4" t="n">
-        <v>974</v>
+        <v>531</v>
       </c>
       <c r="T184" s="4" t="n">
         <v>0</v>
@@ -12951,7 +12981,7 @@
         <v>0</v>
       </c>
       <c r="P185" s="4" t="n">
-        <v>616</v>
+        <v>563</v>
       </c>
       <c r="Q185" s="4" t="n">
         <v>0</v>
@@ -12960,7 +12990,7 @@
         <v>9</v>
       </c>
       <c r="S185" s="4" t="n">
-        <v>635</v>
+        <v>572</v>
       </c>
       <c r="T185" s="4" t="n">
         <v>0</v>
@@ -13019,7 +13049,7 @@
         <v>0</v>
       </c>
       <c r="P186" s="4" t="n">
-        <v>769</v>
+        <v>760</v>
       </c>
       <c r="Q186" s="4" t="n">
         <v>0</v>
@@ -13028,7 +13058,7 @@
         <v>12</v>
       </c>
       <c r="S186" s="4" t="n">
-        <v>781</v>
+        <v>772</v>
       </c>
       <c r="T186" s="4" t="n">
         <v>0</v>
@@ -13223,7 +13253,7 @@
         <v>3</v>
       </c>
       <c r="P189" s="4" t="n">
-        <v>864</v>
+        <v>861</v>
       </c>
       <c r="Q189" s="4" t="n">
         <v>0</v>
@@ -13232,7 +13262,7 @@
         <v>13</v>
       </c>
       <c r="S189" s="4" t="n">
-        <v>877</v>
+        <v>874</v>
       </c>
       <c r="T189" s="4" t="n">
         <v>0</v>
@@ -13359,7 +13389,7 @@
         <v>2</v>
       </c>
       <c r="P191" s="4" t="n">
-        <v>692</v>
+        <v>622</v>
       </c>
       <c r="Q191" s="4" t="n">
         <v>0</v>
@@ -13368,7 +13398,7 @@
         <v>8</v>
       </c>
       <c r="S191" s="4" t="n">
-        <v>700</v>
+        <v>630</v>
       </c>
       <c r="T191" s="4" t="n">
         <v>0</v>
@@ -13631,7 +13661,7 @@
         <v>0</v>
       </c>
       <c r="P195" s="4" t="n">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="Q195" s="4" t="n">
         <v>0</v>
@@ -13640,7 +13670,7 @@
         <v>3</v>
       </c>
       <c r="S195" s="4" t="n">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="T195" s="4" t="n">
         <v>0</v>
@@ -13699,7 +13729,7 @@
         <v>1</v>
       </c>
       <c r="P196" s="4" t="n">
-        <v>900</v>
+        <v>894</v>
       </c>
       <c r="Q196" s="4" t="n">
         <v>0</v>
@@ -13708,7 +13738,7 @@
         <v>1</v>
       </c>
       <c r="S196" s="4" t="n">
-        <v>901</v>
+        <v>895</v>
       </c>
       <c r="T196" s="4" t="n">
         <v>0</v>
@@ -13835,7 +13865,7 @@
         <v>1</v>
       </c>
       <c r="P198" s="4" t="n">
-        <v>359</v>
+        <v>349</v>
       </c>
       <c r="Q198" s="4" t="n">
         <v>0</v>
@@ -13844,7 +13874,7 @@
         <v>6</v>
       </c>
       <c r="S198" s="4" t="n">
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="T198" s="4" t="n">
         <v>0</v>
@@ -13903,7 +13933,7 @@
         <v>1</v>
       </c>
       <c r="P199" s="4" t="n">
-        <v>844</v>
+        <v>839</v>
       </c>
       <c r="Q199" s="4" t="n">
         <v>0</v>
@@ -13912,7 +13942,7 @@
         <v>4</v>
       </c>
       <c r="S199" s="4" t="n">
-        <v>848</v>
+        <v>843</v>
       </c>
       <c r="T199" s="4" t="n">
         <v>0</v>
@@ -13971,7 +14001,7 @@
         <v>3</v>
       </c>
       <c r="P200" s="4" t="n">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="Q200" s="4" t="n">
         <v>0</v>
@@ -13980,7 +14010,7 @@
         <v>10</v>
       </c>
       <c r="S200" s="4" t="n">
-        <v>731</v>
+        <v>728</v>
       </c>
       <c r="T200" s="4" t="n">
         <v>0</v>
@@ -14039,7 +14069,7 @@
         <v>2</v>
       </c>
       <c r="P201" s="4" t="n">
-        <v>716</v>
+        <v>711</v>
       </c>
       <c r="Q201" s="4" t="n">
         <v>0</v>
@@ -14048,7 +14078,7 @@
         <v>40</v>
       </c>
       <c r="S201" s="4" t="n">
-        <v>726</v>
+        <v>751</v>
       </c>
       <c r="T201" s="4" t="n">
         <v>0</v>
@@ -14175,7 +14205,7 @@
         <v>1</v>
       </c>
       <c r="P203" s="4" t="n">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="Q203" s="4" t="n">
         <v>0</v>
@@ -14184,7 +14214,7 @@
         <v>3</v>
       </c>
       <c r="S203" s="4" t="n">
-        <v>551</v>
+        <v>538</v>
       </c>
       <c r="T203" s="4" t="n">
         <v>0</v>
@@ -14243,7 +14273,7 @@
         <v>1</v>
       </c>
       <c r="P204" s="4" t="n">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="Q204" s="4" t="n">
         <v>0</v>
@@ -14252,7 +14282,7 @@
         <v>7</v>
       </c>
       <c r="S204" s="4" t="n">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="T204" s="4" t="n">
         <v>0</v>
@@ -14379,7 +14409,7 @@
         <v>2</v>
       </c>
       <c r="P206" s="4" t="n">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="Q206" s="4" t="n">
         <v>0</v>
@@ -14388,7 +14418,7 @@
         <v>4</v>
       </c>
       <c r="S206" s="4" t="n">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="T206" s="4" t="n">
         <v>0</v>
@@ -14447,7 +14477,7 @@
         <v>0</v>
       </c>
       <c r="P207" s="4" t="n">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="Q207" s="4" t="n">
         <v>0</v>
@@ -14456,7 +14486,7 @@
         <v>12</v>
       </c>
       <c r="S207" s="4" t="n">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="T207" s="4" t="n">
         <v>0</v>
@@ -14524,7 +14554,7 @@
         <v>0</v>
       </c>
       <c r="S208" s="4" t="n">
-        <v>71</v>
+        <v>566</v>
       </c>
       <c r="T208" s="4" t="n">
         <v>0</v>
@@ -14583,7 +14613,7 @@
         <v>1</v>
       </c>
       <c r="P209" s="4" t="n">
-        <v>9</v>
+        <v>509</v>
       </c>
       <c r="Q209" s="4" t="n">
         <v>0</v>
@@ -14652,7 +14682,7 @@
         <v>5</v>
       </c>
       <c r="P210" s="4" t="n">
-        <v>730</v>
+        <v>727</v>
       </c>
       <c r="Q210" s="4" t="n">
         <v>0</v>
@@ -14661,7 +14691,7 @@
         <v>19</v>
       </c>
       <c r="S210" s="4" t="n">
-        <v>749</v>
+        <v>746</v>
       </c>
       <c r="T210" s="4" t="n">
         <v>0</v>
@@ -14720,7 +14750,7 @@
         <v>0</v>
       </c>
       <c r="P211" s="4" t="n">
-        <v>7</v>
+        <v>713</v>
       </c>
       <c r="Q211" s="4" t="n">
         <v>0</v>
@@ -14729,7 +14759,7 @@
         <v>4</v>
       </c>
       <c r="S211" s="4" t="n">
-        <v>71</v>
+        <v>717</v>
       </c>
       <c r="T211" s="4" t="n">
         <v>0</v>
@@ -14856,7 +14886,7 @@
         <v>1</v>
       </c>
       <c r="P213" s="4" t="n">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="Q213" s="4" t="n">
         <v>0</v>
@@ -14865,7 +14895,7 @@
         <v>8</v>
       </c>
       <c r="S213" s="4" t="n">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="T213" s="4" t="n">
         <v>0</v>
@@ -14924,7 +14954,7 @@
         <v>2</v>
       </c>
       <c r="P214" s="4" t="n">
-        <v>735</v>
+        <v>830</v>
       </c>
       <c r="Q214" s="4" t="n">
         <v>0</v>
@@ -14933,7 +14963,7 @@
         <v>4</v>
       </c>
       <c r="S214" s="4" t="n">
-        <v>739</v>
+        <v>834</v>
       </c>
       <c r="T214" s="4" t="n">
         <v>0</v>
@@ -14992,7 +15022,7 @@
         <v>4</v>
       </c>
       <c r="P215" s="4" t="n">
-        <v>817</v>
+        <v>813</v>
       </c>
       <c r="Q215" s="4" t="n">
         <v>0</v>
@@ -15001,7 +15031,7 @@
         <v>6</v>
       </c>
       <c r="S215" s="4" t="n">
-        <v>823</v>
+        <v>819</v>
       </c>
       <c r="T215" s="4" t="n">
         <v>0</v>
@@ -15060,7 +15090,7 @@
         <v>1</v>
       </c>
       <c r="P216" s="4" t="n">
-        <v>538</v>
+        <v>383</v>
       </c>
       <c r="Q216" s="4" t="n">
         <v>0</v>
@@ -15069,7 +15099,7 @@
         <v>6</v>
       </c>
       <c r="S216" s="4" t="n">
-        <v>544</v>
+        <v>389</v>
       </c>
       <c r="T216" s="4" t="n">
         <v>0</v>
@@ -15128,16 +15158,16 @@
         <v>3</v>
       </c>
       <c r="P217" s="4" t="n">
+        <v>806</v>
+      </c>
+      <c r="Q217" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R217" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="S217" s="4" t="n">
         <v>807</v>
-      </c>
-      <c r="Q217" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R217" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="S217" s="4" t="n">
-        <v>818</v>
       </c>
       <c r="T217" s="4" t="n">
         <v>0</v>
@@ -15264,7 +15294,7 @@
         <v>6</v>
       </c>
       <c r="P219" s="4" t="n">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="Q219" s="4" t="n">
         <v>0</v>
@@ -15273,7 +15303,7 @@
         <v>16</v>
       </c>
       <c r="S219" s="4" t="n">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="T219" s="4" t="n">
         <v>0</v>
@@ -15332,7 +15362,7 @@
         <v>2</v>
       </c>
       <c r="P220" s="4" t="n">
-        <v>770</v>
+        <v>763</v>
       </c>
       <c r="Q220" s="4" t="n">
         <v>0</v>
@@ -15341,7 +15371,7 @@
         <v>14</v>
       </c>
       <c r="S220" s="4" t="n">
-        <v>784</v>
+        <v>777</v>
       </c>
       <c r="T220" s="4" t="n">
         <v>0</v>
@@ -15400,7 +15430,7 @@
         <v>4</v>
       </c>
       <c r="P221" s="4" t="n">
-        <v>874</v>
+        <v>872</v>
       </c>
       <c r="Q221" s="4" t="n">
         <v>0</v>
@@ -15409,7 +15439,7 @@
         <v>21</v>
       </c>
       <c r="S221" s="4" t="n">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="T221" s="4" t="n">
         <v>0</v>
@@ -15468,7 +15498,7 @@
         <v>0</v>
       </c>
       <c r="P222" s="4" t="n">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="Q222" s="4" t="n">
         <v>0</v>
@@ -15477,7 +15507,7 @@
         <v>3</v>
       </c>
       <c r="S222" s="4" t="n">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="T222" s="4" t="n">
         <v>0</v>
@@ -15545,7 +15575,7 @@
         <v>1</v>
       </c>
       <c r="S223" s="4" t="n">
-        <v>688</v>
+        <v>678</v>
       </c>
       <c r="T223" s="4" t="n">
         <v>0</v>
@@ -15604,7 +15634,7 @@
         <v>5</v>
       </c>
       <c r="P224" s="4" t="n">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="Q224" s="4" t="n">
         <v>0</v>
@@ -15613,7 +15643,7 @@
         <v>10</v>
       </c>
       <c r="S224" s="4" t="n">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="T224" s="4" t="n">
         <v>0</v>
@@ -15672,7 +15702,7 @@
         <v>5</v>
       </c>
       <c r="P225" s="4" t="n">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="Q225" s="4" t="n">
         <v>0</v>
@@ -15681,7 +15711,7 @@
         <v>8</v>
       </c>
       <c r="S225" s="4" t="n">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="T225" s="4" t="n">
         <v>0</v>
@@ -15740,7 +15770,7 @@
         <v>0</v>
       </c>
       <c r="P226" s="4" t="n">
-        <v>589</v>
+        <v>536</v>
       </c>
       <c r="Q226" s="4" t="n">
         <v>0</v>
@@ -15749,7 +15779,7 @@
         <v>8</v>
       </c>
       <c r="S226" s="4" t="n">
-        <v>597</v>
+        <v>544</v>
       </c>
       <c r="T226" s="4" t="n">
         <v>0</v>
@@ -15808,7 +15838,7 @@
         <v>4</v>
       </c>
       <c r="P227" s="4" t="n">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="Q227" s="4" t="n">
         <v>0</v>
@@ -15817,7 +15847,7 @@
         <v>6</v>
       </c>
       <c r="S227" s="4" t="n">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="T227" s="4" t="n">
         <v>0</v>
@@ -15876,7 +15906,7 @@
         <v>7</v>
       </c>
       <c r="P228" s="4" t="n">
-        <v>858</v>
+        <v>788</v>
       </c>
       <c r="Q228" s="4" t="n">
         <v>0</v>
@@ -15885,7 +15915,7 @@
         <v>23</v>
       </c>
       <c r="S228" s="4" t="n">
-        <v>881</v>
+        <v>811</v>
       </c>
       <c r="T228" s="4" t="n">
         <v>0</v>
@@ -16080,7 +16110,7 @@
         <v>1</v>
       </c>
       <c r="P231" s="4" t="n">
-        <v>513</v>
+        <v>463</v>
       </c>
       <c r="Q231" s="4" t="n">
         <v>0</v>
@@ -16089,7 +16119,7 @@
         <v>18</v>
       </c>
       <c r="S231" s="4" t="n">
-        <v>531</v>
+        <v>481</v>
       </c>
       <c r="T231" s="4" t="n">
         <v>0</v>
@@ -16148,7 +16178,7 @@
         <v>0</v>
       </c>
       <c r="P232" s="4" t="n">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="Q232" s="4" t="n">
         <v>0</v>
@@ -16157,7 +16187,7 @@
         <v>4</v>
       </c>
       <c r="S232" s="4" t="n">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="T232" s="4" t="n">
         <v>0</v>
@@ -16216,7 +16246,7 @@
         <v>0</v>
       </c>
       <c r="P233" s="4" t="n">
-        <v>525</v>
+        <v>512</v>
       </c>
       <c r="Q233" s="4" t="n">
         <v>0</v>
@@ -16225,7 +16255,7 @@
         <v>5</v>
       </c>
       <c r="S233" s="4" t="n">
-        <v>530</v>
+        <v>517</v>
       </c>
       <c r="T233" s="4" t="n">
         <v>0</v>
@@ -16293,7 +16323,7 @@
         <v>0</v>
       </c>
       <c r="S234" s="4" t="n">
-        <v>589</v>
+        <v>582</v>
       </c>
       <c r="T234" s="4" t="n">
         <v>0</v>
@@ -16352,7 +16382,7 @@
         <v>3</v>
       </c>
       <c r="P235" s="4" t="n">
-        <v>706</v>
+        <v>696</v>
       </c>
       <c r="Q235" s="4" t="n">
         <v>0</v>
@@ -16361,7 +16391,7 @@
         <v>9</v>
       </c>
       <c r="S235" s="4" t="n">
-        <v>715</v>
+        <v>705</v>
       </c>
       <c r="T235" s="4" t="n">
         <v>0</v>
@@ -16556,7 +16586,7 @@
         <v>0</v>
       </c>
       <c r="P238" s="4" t="n">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="Q238" s="4" t="n">
         <v>0</v>
@@ -16565,7 +16595,7 @@
         <v>6</v>
       </c>
       <c r="S238" s="4" t="n">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="T238" s="4" t="n">
         <v>0</v>
@@ -16692,7 +16722,7 @@
         <v>1</v>
       </c>
       <c r="P240" s="4" t="n">
-        <v>501</v>
+        <v>448</v>
       </c>
       <c r="Q240" s="4" t="n">
         <v>0</v>
@@ -16701,7 +16731,7 @@
         <v>17</v>
       </c>
       <c r="S240" s="4" t="n">
-        <v>518</v>
+        <v>465</v>
       </c>
       <c r="T240" s="4" t="n">
         <v>0</v>
@@ -16769,7 +16799,7 @@
         <v>2</v>
       </c>
       <c r="S241" s="4" t="n">
-        <v>795</v>
+        <v>772</v>
       </c>
       <c r="T241" s="4" t="n">
         <v>0</v>
@@ -16828,7 +16858,7 @@
         <v>1</v>
       </c>
       <c r="P242" s="4" t="n">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="Q242" s="4" t="n">
         <v>0</v>
@@ -16837,7 +16867,7 @@
         <v>10</v>
       </c>
       <c r="S242" s="4" t="n">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="T242" s="4" t="n">
         <v>0</v>
@@ -16965,7 +16995,7 @@
         <v>1</v>
       </c>
       <c r="P244" s="4" t="n">
-        <v>960</v>
+        <v>953</v>
       </c>
       <c r="Q244" s="4" t="n">
         <v>0</v>
@@ -16974,7 +17004,7 @@
         <v>9</v>
       </c>
       <c r="S244" s="4" t="n">
-        <v>969</v>
+        <v>962</v>
       </c>
       <c r="T244" s="4" t="n">
         <v>0</v>
@@ -17043,7 +17073,7 @@
         <v>1</v>
       </c>
       <c r="S245" s="4" t="n">
-        <v>744</v>
+        <v>734</v>
       </c>
       <c r="T245" s="4" t="n">
         <v>0</v>
@@ -17103,7 +17133,7 @@
         <v>4</v>
       </c>
       <c r="P246" s="4" t="n">
-        <v>638</v>
+        <v>630</v>
       </c>
       <c r="Q246" s="4" t="n">
         <v>0</v>
@@ -17112,7 +17142,7 @@
         <v>7</v>
       </c>
       <c r="S246" s="4" t="n">
-        <v>645</v>
+        <v>637</v>
       </c>
       <c r="T246" s="4" t="n">
         <v>0</v>
@@ -17239,7 +17269,7 @@
         <v>0</v>
       </c>
       <c r="P248" s="4" t="n">
-        <v>924</v>
+        <v>919</v>
       </c>
       <c r="Q248" s="4" t="n">
         <v>0</v>
@@ -17248,7 +17278,7 @@
         <v>3</v>
       </c>
       <c r="S248" s="4" t="n">
-        <v>927</v>
+        <v>922</v>
       </c>
       <c r="T248" s="4" t="n">
         <v>0</v>
@@ -17307,7 +17337,7 @@
         <v>2</v>
       </c>
       <c r="P249" s="4" t="n">
-        <v>977</v>
+        <v>974</v>
       </c>
       <c r="Q249" s="4" t="n">
         <v>0</v>
@@ -17316,7 +17346,7 @@
         <v>8</v>
       </c>
       <c r="S249" s="4" t="n">
-        <v>985</v>
+        <v>982</v>
       </c>
       <c r="T249" s="4" t="n">
         <v>0</v>
@@ -17443,7 +17473,7 @@
         <v>2</v>
       </c>
       <c r="P251" s="4" t="n">
-        <v>14</v>
+        <v>77</v>
       </c>
       <c r="Q251" s="4" t="n">
         <v>1</v>
@@ -17452,7 +17482,7 @@
         <v>16</v>
       </c>
       <c r="S251" s="4" t="n">
-        <v>17</v>
+        <v>94</v>
       </c>
       <c r="T251" s="4" t="n">
         <v>18</v>
@@ -17520,7 +17550,7 @@
         <v>0</v>
       </c>
       <c r="S252" s="4" t="n">
-        <v>77</v>
+        <v>715</v>
       </c>
       <c r="T252" s="4" t="n">
         <v>0</v>
@@ -17579,7 +17609,7 @@
         <v>2</v>
       </c>
       <c r="P253" s="4" t="n">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="Q253" s="4" t="n">
         <v>0</v>
@@ -17588,7 +17618,7 @@
         <v>10</v>
       </c>
       <c r="S253" s="4" t="n">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="T253" s="4" t="n">
         <v>0</v>
@@ -17647,7 +17677,7 @@
         <v>1</v>
       </c>
       <c r="P254" s="4" t="n">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="Q254" s="4" t="n">
         <v>0</v>
@@ -17656,7 +17686,7 @@
         <v>4</v>
       </c>
       <c r="S254" s="4" t="n">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="T254" s="4" t="n">
         <v>0</v>
@@ -17715,7 +17745,7 @@
         <v>1</v>
       </c>
       <c r="P255" s="4" t="n">
-        <v>328</v>
+        <v>250</v>
       </c>
       <c r="Q255" s="4" t="n">
         <v>0</v>
@@ -17724,7 +17754,7 @@
         <v>3</v>
       </c>
       <c r="S255" s="4" t="n">
-        <v>331</v>
+        <v>253</v>
       </c>
       <c r="T255" s="4" t="n">
         <v>0</v>
@@ -17783,7 +17813,7 @@
         <v>1</v>
       </c>
       <c r="P256" s="4" t="n">
-        <v>665</v>
+        <v>657</v>
       </c>
       <c r="Q256" s="4" t="n">
         <v>0</v>
@@ -17792,7 +17822,7 @@
         <v>10</v>
       </c>
       <c r="S256" s="4" t="n">
-        <v>675</v>
+        <v>667</v>
       </c>
       <c r="T256" s="4" t="n">
         <v>0</v>
@@ -17860,7 +17890,7 @@
         <v>0</v>
       </c>
       <c r="S257" s="4" t="n">
-        <v>810</v>
+        <v>803</v>
       </c>
       <c r="T257" s="4" t="n">
         <v>0</v>
@@ -17987,7 +18017,7 @@
         <v>3</v>
       </c>
       <c r="P259" s="4" t="n">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="Q259" s="4" t="n">
         <v>0</v>
@@ -17996,7 +18026,7 @@
         <v>7</v>
       </c>
       <c r="S259" s="4" t="n">
-        <v>789</v>
+        <v>786</v>
       </c>
       <c r="T259" s="4" t="n">
         <v>0</v>
@@ -18123,7 +18153,7 @@
         <v>1</v>
       </c>
       <c r="P261" s="4" t="n">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="Q261" s="4" t="n">
         <v>0</v>
@@ -18132,7 +18162,7 @@
         <v>8</v>
       </c>
       <c r="S261" s="4" t="n">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="T261" s="4" t="n">
         <v>0</v>
@@ -18211,234 +18241,234 @@
       </c>
     </row>
     <row r="263">
-      <c r="A263" s="7" t="inlineStr">
+      <c r="A263" s="18" t="inlineStr">
         <is>
           <t>TOTAL EVM VOTES</t>
         </is>
       </c>
-      <c r="B263" s="15" t="inlineStr"/>
-      <c r="C263" s="8">
+      <c r="B263" s="19" t="inlineStr"/>
+      <c r="C263" s="20">
         <f>SUM(C6:C262)</f>
         <v/>
       </c>
-      <c r="D263" s="8">
+      <c r="D263" s="20">
         <f>SUM(D6:D262)</f>
         <v/>
       </c>
-      <c r="E263" s="8">
+      <c r="E263" s="20">
         <f>SUM(E6:E262)</f>
         <v/>
       </c>
-      <c r="F263" s="8">
+      <c r="F263" s="20">
         <f>SUM(F6:F262)</f>
         <v/>
       </c>
-      <c r="G263" s="8">
+      <c r="G263" s="20">
         <f>SUM(G6:G262)</f>
         <v/>
       </c>
-      <c r="H263" s="8">
+      <c r="H263" s="20">
         <f>SUM(H6:H262)</f>
         <v/>
       </c>
-      <c r="I263" s="8">
+      <c r="I263" s="20">
         <f>SUM(I6:I262)</f>
         <v/>
       </c>
-      <c r="J263" s="8">
+      <c r="J263" s="20">
         <f>SUM(J6:J262)</f>
         <v/>
       </c>
-      <c r="K263" s="8">
+      <c r="K263" s="20">
         <f>SUM(K6:K262)</f>
         <v/>
       </c>
-      <c r="L263" s="8">
+      <c r="L263" s="20">
         <f>SUM(L6:L262)</f>
         <v/>
       </c>
-      <c r="M263" s="8">
+      <c r="M263" s="20">
         <f>SUM(M6:M262)</f>
         <v/>
       </c>
-      <c r="N263" s="8">
+      <c r="N263" s="20">
         <f>SUM(N6:N262)</f>
         <v/>
       </c>
-      <c r="O263" s="8">
+      <c r="O263" s="20">
         <f>SUM(O6:O262)</f>
         <v/>
       </c>
-      <c r="P263" s="8">
+      <c r="P263" s="20">
         <f>SUM(P6:P262)</f>
         <v/>
       </c>
-      <c r="Q263" s="8">
+      <c r="Q263" s="20">
         <f>SUM(Q6:Q262)</f>
         <v/>
       </c>
-      <c r="R263" s="8">
+      <c r="R263" s="20">
         <f>SUM(R6:R262)</f>
         <v/>
       </c>
-      <c r="S263" s="8">
+      <c r="S263" s="20">
         <f>SUM(S6:S262)</f>
         <v/>
       </c>
-      <c r="T263" s="8">
+      <c r="T263" s="20">
         <f>SUM(T6:T262)</f>
         <v/>
       </c>
-      <c r="U263" s="8">
+      <c r="U263" s="20">
         <f>SUM(U6:U262)</f>
         <v/>
       </c>
     </row>
     <row r="264">
-      <c r="A264" s="9" t="inlineStr">
+      <c r="A264" s="21" t="inlineStr">
         <is>
           <t>POSTAL BALLOT VOTES</t>
         </is>
       </c>
       <c r="B264" s="16" t="inlineStr"/>
-      <c r="C264" s="10" t="n">
+      <c r="C264" s="20" t="n">
         <v>279</v>
       </c>
-      <c r="D264" s="10" t="n">
+      <c r="D264" s="20" t="n">
         <v>21</v>
       </c>
-      <c r="E264" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="F264" s="10" t="n">
+      <c r="E264" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="F264" s="20" t="n">
         <v>10</v>
       </c>
-      <c r="G264" s="10" t="n">
+      <c r="G264" s="20" t="n">
         <v>107</v>
       </c>
-      <c r="H264" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I264" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J264" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K264" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L264" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M264" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N264" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O264" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P264" s="10" t="n">
+      <c r="H264" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I264" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J264" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K264" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L264" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M264" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N264" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O264" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P264" s="20" t="n">
         <v>420</v>
       </c>
-      <c r="Q264" s="10" t="n">
+      <c r="Q264" s="20" t="n">
         <v>47</v>
       </c>
-      <c r="R264" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="S264" s="10" t="n">
+      <c r="R264" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="S264" s="20" t="n">
         <v>470</v>
       </c>
-      <c r="T264" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U264" s="10" t="n">
+      <c r="T264" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U264" s="20" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="265">
-      <c r="A265" s="11" t="inlineStr">
+      <c r="A265" s="22" t="inlineStr">
         <is>
           <t>TOTAL VOTES POLLED</t>
         </is>
       </c>
-      <c r="B265" s="17" t="inlineStr"/>
-      <c r="C265" s="12">
+      <c r="B265" s="23" t="inlineStr"/>
+      <c r="C265" s="24">
         <f>C263+C264</f>
         <v/>
       </c>
-      <c r="D265" s="12">
+      <c r="D265" s="24">
         <f>D263+D264</f>
         <v/>
       </c>
-      <c r="E265" s="12">
+      <c r="E265" s="24">
         <f>E263+E264</f>
         <v/>
       </c>
-      <c r="F265" s="12">
+      <c r="F265" s="24">
         <f>F263+F264</f>
         <v/>
       </c>
-      <c r="G265" s="12">
+      <c r="G265" s="24">
         <f>G263+G264</f>
         <v/>
       </c>
-      <c r="H265" s="12">
+      <c r="H265" s="24">
         <f>H263+H264</f>
         <v/>
       </c>
-      <c r="I265" s="12">
+      <c r="I265" s="24">
         <f>I263+I264</f>
         <v/>
       </c>
-      <c r="J265" s="12">
+      <c r="J265" s="24">
         <f>J263+J264</f>
         <v/>
       </c>
-      <c r="K265" s="12">
+      <c r="K265" s="24">
         <f>K263+K264</f>
         <v/>
       </c>
-      <c r="L265" s="12">
+      <c r="L265" s="24">
         <f>L263+L264</f>
         <v/>
       </c>
-      <c r="M265" s="12">
+      <c r="M265" s="24">
         <f>M263+M264</f>
         <v/>
       </c>
-      <c r="N265" s="12">
+      <c r="N265" s="24">
         <f>N263+N264</f>
         <v/>
       </c>
-      <c r="O265" s="12">
+      <c r="O265" s="24">
         <f>O263+O264</f>
         <v/>
       </c>
-      <c r="P265" s="12">
+      <c r="P265" s="24">
         <f>P263+P264</f>
         <v/>
       </c>
-      <c r="Q265" s="12">
+      <c r="Q265" s="24">
         <f>Q263+Q264</f>
         <v/>
       </c>
-      <c r="R265" s="12">
+      <c r="R265" s="24">
         <f>R263+R264</f>
         <v/>
       </c>
-      <c r="S265" s="12">
+      <c r="S265" s="24">
         <f>S263+S264</f>
         <v/>
       </c>
-      <c r="T265" s="12">
+      <c r="T265" s="24">
         <f>T263+T264</f>
         <v/>
       </c>
-      <c r="U265" s="12">
+      <c r="U265" s="24">
         <f>U263+U264</f>
         <v/>
       </c>
